--- a/data/trans_orig/IQ3003_MoAR-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ3003_MoAR-Habitat-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la edad en meses en la que empezaron a comer fruta</t>
+          <t>Menores según la edad en meses en la que empezaron a comer fruta (tasa de respuesta: 68,24%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,75; 5,51</t>
+          <t>4,76; 5,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,46; 6,34</t>
+          <t>5,46; 6,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,93; 6,5</t>
+          <t>4,86; 6,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,78; 5,64</t>
+          <t>4,81; 5,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,03; 6,54</t>
+          <t>5,05; 6,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,24; 6,26</t>
+          <t>5,26; 6,28</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,87; 5,45</t>
+          <t>4,87; 5,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,37; 6,24</t>
+          <t>5,36; 6,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,27; 6,11</t>
+          <t>5,28; 6,16</t>
         </is>
       </c>
     </row>
@@ -787,42 +787,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,86; 5,73</t>
+          <t>4,87; 5,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,05; 6,0</t>
+          <t>5,06; 5,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,23; 6,07</t>
+          <t>5,24; 6,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,77; 5,6</t>
+          <t>4,79; 5,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,46; 6,57</t>
+          <t>5,42; 6,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,78; 5,8</t>
+          <t>4,82; 5,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,93; 5,49</t>
+          <t>4,88; 5,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,35; 6,11</t>
+          <t>5,38; 6,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,82; 5,64</t>
+          <t>4,81; 5,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,11; 6,27</t>
+          <t>5,1; 6,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,29; 6,62</t>
+          <t>5,27; 6,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,78; 5,99</t>
+          <t>4,83; 6,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,75; 5,78</t>
+          <t>4,79; 5,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,69; 8,33</t>
+          <t>5,68; 8,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,97; 5,72</t>
+          <t>4,94; 5,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,08; 5,82</t>
+          <t>5,1; 5,82</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,62; 7,21</t>
+          <t>5,63; 7,22</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,52; 5,61</t>
+          <t>4,48; 5,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,23; 8,18</t>
+          <t>5,29; 8,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,83; 7,47</t>
+          <t>5,91; 7,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,96; 6,2</t>
+          <t>4,97; 6,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,31; 6,71</t>
+          <t>5,34; 6,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,09; 5,99</t>
+          <t>5,06; 5,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,84; 5,62</t>
+          <t>4,84; 5,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,46; 7,15</t>
+          <t>5,49; 7,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,7; 6,78</t>
+          <t>5,72; 6,78</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,86; 5,4</t>
+          <t>4,89; 5,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,42; 6,5</t>
+          <t>5,42; 6,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,64; 6,34</t>
+          <t>5,64; 6,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,03; 5,54</t>
+          <t>5,04; 5,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,44; 6,05</t>
+          <t>5,42; 6,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,4; 6,12</t>
+          <t>5,42; 6,12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,02; 5,38</t>
+          <t>5,02; 5,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,51; 6,15</t>
+          <t>5,51; 6,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,6; 6,12</t>
+          <t>5,61; 6,09</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3003_MoAR-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ3003_MoAR-Habitat-trans_orig.xlsx
@@ -677,7 +677,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,76; 5,51</t>
+          <t>4,75; 5,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -687,37 +687,37 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,86; 6,42</t>
+          <t>4,88; 6,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,81; 5,65</t>
+          <t>4,84; 5,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,05; 6,54</t>
+          <t>5,06; 6,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,26; 6,28</t>
+          <t>5,22; 6,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,87; 5,47</t>
+          <t>4,86; 5,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,36; 6,24</t>
+          <t>5,34; 6,18</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,28; 6,16</t>
+          <t>5,24; 6,13</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,87; 5,75</t>
+          <t>4,88; 5,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,06; 5,94</t>
+          <t>5,05; 6,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,24; 6,1</t>
+          <t>5,23; 6,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,79; 5,6</t>
+          <t>4,76; 5,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,42; 6,56</t>
+          <t>5,41; 6,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,82; 5,81</t>
+          <t>4,8; 5,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,88; 5,45</t>
+          <t>4,9; 5,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,38; 6,14</t>
+          <t>5,35; 6,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,12; 5,76</t>
+          <t>5,11; 5,77</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,81; 5,66</t>
+          <t>4,82; 5,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,1; 6,27</t>
+          <t>5,14; 6,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,27; 6,76</t>
+          <t>5,3; 6,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,83; 6,0</t>
+          <t>4,79; 6,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,79; 5,77</t>
+          <t>4,78; 5,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,68; 8,26</t>
+          <t>5,65; 8,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,94; 5,68</t>
+          <t>4,93; 5,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,1; 5,82</t>
+          <t>5,09; 5,81</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,63; 7,22</t>
+          <t>5,62; 7,08</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,48; 5,6</t>
+          <t>4,45; 5,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,29; 8,49</t>
+          <t>5,28; 8,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,91; 7,5</t>
+          <t>5,89; 7,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,97; 6,18</t>
+          <t>4,98; 6,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,34; 6,67</t>
+          <t>5,29; 6,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,06; 5,95</t>
+          <t>5,06; 5,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,84; 5,64</t>
+          <t>4,85; 5,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,49; 7,25</t>
+          <t>5,47; 7,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,72; 6,78</t>
+          <t>5,72; 6,79</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,89; 5,4</t>
+          <t>4,88; 5,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,42; 6,55</t>
+          <t>5,43; 6,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,64; 6,37</t>
+          <t>5,63; 6,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,04; 5,59</t>
+          <t>5,04; 5,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,42; 6,1</t>
+          <t>5,43; 6,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,42; 6,12</t>
+          <t>5,45; 6,09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,02; 5,39</t>
+          <t>5,05; 5,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,51; 6,11</t>
+          <t>5,51; 6,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,61; 6,09</t>
+          <t>5,62; 6,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3003_MoAR-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ3003_MoAR-Habitat-trans_orig.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5,2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5,61</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5,75</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>5,1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>5,85</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>5,56</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5,2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,61</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5,75</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,75; 5,55</t>
+          <t>4,78; 5,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,46; 6,36</t>
+          <t>5,03; 6,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,88; 6,44</t>
+          <t>5,24; 6,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,84; 5,65</t>
+          <t>4,75; 5,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,06; 6,49</t>
+          <t>5,46; 6,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,22; 6,22</t>
+          <t>4,93; 6,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,86; 5,47</t>
+          <t>4,87; 5,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,34; 6,18</t>
+          <t>5,37; 6,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,24; 6,13</t>
+          <t>5,27; 6,11</t>
         </is>
       </c>
     </row>
@@ -734,32 +734,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>5,1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5,89</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5,26</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>5,22</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>5,45</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>5,62</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5,1</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,89</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,26</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,88; 5,82</t>
+          <t>4,77; 5,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>5,46; 6,57</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4,78; 5,8</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4,86; 5,73</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>5,05; 6,0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>5,23; 6,09</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4,76; 5,57</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>5,41; 6,52</t>
-        </is>
-      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,8; 5,78</t>
+          <t>5,23; 6,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,9; 5,49</t>
+          <t>4,93; 5,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,35; 6,1</t>
+          <t>5,35; 6,11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,11; 5,77</t>
+          <t>5,12; 5,76</t>
         </is>
       </c>
     </row>
@@ -844,32 +844,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5,37</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5,31</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6,68</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>5,22</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>5,54</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>5,74</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,37</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5,31</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>6,68</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,82; 5,68</t>
+          <t>4,78; 5,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,14; 6,28</t>
+          <t>4,75; 5,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,3; 6,66</t>
+          <t>5,69; 8,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,79; 6,0</t>
+          <t>4,82; 5,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,78; 5,86</t>
+          <t>5,11; 6,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,65; 8,26</t>
+          <t>5,29; 6,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,93; 5,67</t>
+          <t>4,97; 5,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,09; 5,81</t>
+          <t>5,08; 5,82</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,62; 7,08</t>
+          <t>5,62; 7,21</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5,46</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5,85</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5,53</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>4,97</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>6,04</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>6,53</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5,46</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,85</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,53</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,45; 5,58</t>
+          <t>4,96; 6,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,28; 8,48</t>
+          <t>5,31; 6,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,89; 7,53</t>
+          <t>5,09; 5,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,98; 6,2</t>
+          <t>4,52; 5,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,29; 6,65</t>
+          <t>5,23; 8,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,06; 5,93</t>
+          <t>5,83; 7,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,85; 5,63</t>
+          <t>4,84; 5,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,47; 7,31</t>
+          <t>5,46; 7,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,72; 6,79</t>
+          <t>5,7; 6,78</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>5,29</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5,71</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5,73</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>5,11</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>5,74</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>5,95</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5,29</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>5,71</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,73</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,88; 5,36</t>
+          <t>5,03; 5,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,43; 6,69</t>
+          <t>5,44; 6,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,63; 6,35</t>
+          <t>5,4; 6,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,04; 5,6</t>
+          <t>4,86; 5,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,43; 6,1</t>
+          <t>5,42; 6,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,45; 6,09</t>
+          <t>5,64; 6,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,05; 5,4</t>
+          <t>5,02; 5,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,51; 6,12</t>
+          <t>5,51; 6,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,62; 6,13</t>
+          <t>5,6; 6,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3003_MoAR-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ3003_MoAR-Habitat-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -523,7 +528,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la edad en meses en la que empezaron a comer fruta (tasa de respuesta: 68,24%)</t>
+          <t>Edad media en meses a la que los menores empezaron a comer fruta (tasa de respuesta: 68,24%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -622,329 +627,217 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>5,2</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>5,61</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5,75</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5,1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,85</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5,56</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,16</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5,72</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5,69</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>5.202078790909597</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>5.609382412405484</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>5.753613660707565</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>5.095409130678826</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>5.851336362221931</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>5.561623552751444</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>5.156432578067741</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>5.717899765521581</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>5.685103273933175</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>4,78; 5,64</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>5,03; 6,54</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5,24; 6,26</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4,75; 5,51</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>5,46; 6,34</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>4,93; 6,5</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>4,87; 5,45</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>5,37; 6,24</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>5,27; 6,11</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>4.780378907050889</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>5.031148935390998</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>5.241909728998709</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>4.750591045243374</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>5.461947458606864</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>4.93394164457384</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>4.869246784135355</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>5.366971901430546</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>5.273026864285414</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>5.642857069253101</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>6.535066355454</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>6.264893549744774</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>5.507270334107058</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>6.342318556546308</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>6.496199311693812</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>5.450961317420398</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>6.238434237551878</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>6.107213876375881</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>5,1</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>5,89</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5,26</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5,22</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,45</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,62</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>5,15</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>5,68</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>5,44</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>4,77; 5,6</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>5,46; 6,57</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4,78; 5,8</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4,86; 5,73</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>5,05; 6,0</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5,23; 6,07</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,93; 5,49</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5,35; 6,11</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>5,12; 5,76</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>5.101070398471724</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>5.889645389332821</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>5.262378641929758</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>5.223103831889624</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>5.44946808996452</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>5.624650407485774</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>5.154844176287816</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>5.684217830331209</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>5.441068706459194</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>5,37</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>5,31</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6,68</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,22</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5,54</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,74</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5,29</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>5,43</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>6,22</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>4.765563814361857</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>5.457671906429002</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>4.780923787029148</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>4.862621841831829</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>5.047520970964753</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>5.227228095487995</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>4.926966639217171</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>5.352817270055244</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>5.123586771547743</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>4,78; 5,99</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>4,75; 5,78</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>5,69; 8,33</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>4,82; 5,64</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>5,11; 6,27</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>5,29; 6,62</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>4,97; 5,72</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>5,08; 5,82</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>5,62; 7,21</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>5.604060096512544</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>6.569762063433022</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>5.795988126158778</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>5.730875718243071</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>5.998710323337506</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>6.074790087950532</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>5.492648943413508</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>6.11246633308804</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>5.760135522581029</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -952,217 +845,324 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>5,46</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5,85</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>5,53</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,97</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6,04</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,53</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,21</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5,95</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>6,14</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>5.367061361561851</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>5.308255029734185</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>6.679294139172132</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>5.218155544913105</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>5.537373508081404</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>5.743624127415196</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>5.29127548629946</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>5.431458057978879</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>6.21927097144105</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>4,96; 6,2</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>5,31; 6,71</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>5,09; 5,99</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>4,52; 5,61</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>5,23; 8,18</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>5,83; 7,47</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4,84; 5,62</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>5,46; 7,15</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>5,7; 6,78</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>4.782559046451902</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>4.75262797863454</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>5.691640804387538</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>4.82132472900638</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>5.108165778017696</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>5.289119979446735</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>4.973023283701612</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>5.082361048474492</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>5.624159718099191</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>5.993386285662924</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>5.783157941480502</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>8.330432053477486</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>5.637620378734122</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>6.267735570510285</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>6.621010573549459</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>5.71669398800811</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>5.818321070134703</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>7.212478135932513</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>5.459940744141471</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>5.853971529727946</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>5.527878690912374</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>4.973743226632629</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>6.038815675870247</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>6.527935051532847</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>5.210823185115553</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>5.950592103834614</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>6.141419712955269</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>4.964275426205578</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>5.310198962870311</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>5.087148180439179</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>4.51572038185171</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>5.22836088485</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>5.82804793039188</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>4.838771219411473</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>5.459685351936027</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>5.700167551157081</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>6.200805117679221</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>6.713758890055042</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>5.991500320429474</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>5.607056199501699</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>8.175692735661395</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>7.46916895762786</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>5.62038689761213</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>7.147823503516293</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>6.784733468291847</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>5,29</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>5,71</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>5,73</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5,11</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>5,74</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,95</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>5,2</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>5,72</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>5,84</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>5,03; 5,54</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>5,44; 6,05</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5,4; 6,12</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4,86; 5,4</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>5,42; 6,5</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>5,64; 6,34</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,02; 5,38</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5,51; 6,15</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>5,6; 6,12</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>5.287236535993147</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>5.710595214729491</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>5.729992355479321</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>5.106738958104593</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>5.73521642629132</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>5.95198247770825</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>5.201199985918977</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>5.722800920856931</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>5.840283022859533</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>5.031902862230594</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>5.441791039025824</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>5.396243719132714</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>4.864914916957367</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>5.417174316414541</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>5.642872783485523</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>5.023719663340888</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>5.510421456459165</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>5.601660424482842</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>5.542318412185906</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>6.051160146706757</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>6.116072155068721</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>5.395361279422414</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>6.504168994692128</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>6.342453230769372</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>5.384873981214119</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>6.147643096744976</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>6.123516646260975</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1171,14 +1171,14 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
